--- a/OHC_ensemble/observ_late/NCEILevitus/ohca_NCEILevitus.xlsx
+++ b/OHC_ensemble/observ_late/NCEILevitus/ohca_NCEILevitus.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/OHC_ensemble/observ_late/NCEI:Levitus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/OHC_ensemble/observ_late/NCEILevitus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF05323-4D46-2E40-82AE-F42F30ACB7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CBDC77-5187-D947-9303-5F98ACECB683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="1700" windowWidth="27640" windowHeight="16940" xr2:uid="{15B93CAD-0033-5041-A59B-8625066734DF}"/>
+    <workbookView xWindow="9640" yWindow="1480" windowWidth="27640" windowHeight="16940" xr2:uid="{15B93CAD-0033-5041-A59B-8625066734DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,6 +39,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -103,6 +131,628 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="yearl_h22_se_WO"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1">
+            <v>1.7</v>
+          </cell>
+          <cell r="B1">
+            <v>0.71899999999999997</v>
+          </cell>
+          <cell r="C1">
+            <v>0.39600000000000002</v>
+          </cell>
+          <cell r="D1">
+            <v>0.68700000000000006</v>
+          </cell>
+          <cell r="E1">
+            <v>0.86299999999999999</v>
+          </cell>
+          <cell r="F1">
+            <v>0.499</v>
+          </cell>
+          <cell r="G1">
+            <v>0.42099999999999999</v>
+          </cell>
+          <cell r="H1">
+            <v>0.94699999999999995</v>
+          </cell>
+          <cell r="I1">
+            <v>0.65</v>
+          </cell>
+          <cell r="J1">
+            <v>0.92200000000000004</v>
+          </cell>
+          <cell r="K1">
+            <v>0.307</v>
+          </cell>
+          <cell r="L1">
+            <v>0.45600000000000002</v>
+          </cell>
+          <cell r="M1">
+            <v>0.372</v>
+          </cell>
+          <cell r="N1">
+            <v>0.85799999999999998</v>
+          </cell>
+          <cell r="O1">
+            <v>0.53300000000000003</v>
+          </cell>
+          <cell r="P1">
+            <v>0.86199999999999999</v>
+          </cell>
+          <cell r="Q1">
+            <v>0.51</v>
+          </cell>
+          <cell r="R1">
+            <v>1.1539999999999999</v>
+          </cell>
+          <cell r="S1">
+            <v>1.256</v>
+          </cell>
+          <cell r="T1">
+            <v>0.72899999999999998</v>
+          </cell>
+          <cell r="U1">
+            <v>0.46700000000000003</v>
+          </cell>
+          <cell r="V1">
+            <v>0.61599999999999999</v>
+          </cell>
+          <cell r="W1">
+            <v>0.71699999999999997</v>
+          </cell>
+          <cell r="X1">
+            <v>0.432</v>
+          </cell>
+          <cell r="Y1">
+            <v>0.5</v>
+          </cell>
+          <cell r="Z1">
+            <v>0.42199999999999999</v>
+          </cell>
+          <cell r="AA1">
+            <v>0.54900000000000004</v>
+          </cell>
+          <cell r="AB1">
+            <v>0.91600000000000004</v>
+          </cell>
+          <cell r="AC1">
+            <v>1.871</v>
+          </cell>
+          <cell r="AD1">
+            <v>1.262</v>
+          </cell>
+          <cell r="AE1">
+            <v>1.2270000000000001</v>
+          </cell>
+          <cell r="AF1">
+            <v>1.109</v>
+          </cell>
+          <cell r="AG1">
+            <v>0.53100000000000003</v>
+          </cell>
+          <cell r="AH1">
+            <v>0.42199999999999999</v>
+          </cell>
+          <cell r="AI1">
+            <v>0.52100000000000002</v>
+          </cell>
+          <cell r="AJ1">
+            <v>0.90600000000000003</v>
+          </cell>
+          <cell r="AK1">
+            <v>0.28100000000000003</v>
+          </cell>
+          <cell r="AL1">
+            <v>0.35799999999999998</v>
+          </cell>
+          <cell r="AM1">
+            <v>0.439</v>
+          </cell>
+          <cell r="AN1">
+            <v>0.746</v>
+          </cell>
+          <cell r="AO1">
+            <v>0.64900000000000002</v>
+          </cell>
+          <cell r="AP1">
+            <v>1.0649999999999999</v>
+          </cell>
+          <cell r="AQ1">
+            <v>0.53900000000000003</v>
+          </cell>
+          <cell r="AR1">
+            <v>0.55700000000000005</v>
+          </cell>
+          <cell r="AS1">
+            <v>0.26900000000000002</v>
+          </cell>
+          <cell r="AT1">
+            <v>0.53200000000000003</v>
+          </cell>
+          <cell r="AU1">
+            <v>1.115</v>
+          </cell>
+          <cell r="AV1">
+            <v>0.52300000000000002</v>
+          </cell>
+          <cell r="AW1">
+            <v>0.622</v>
+          </cell>
+          <cell r="AX1">
+            <v>0.28299999999999997</v>
+          </cell>
+          <cell r="AY1">
+            <v>0.317</v>
+          </cell>
+          <cell r="AZ1">
+            <v>0.19900000000000001</v>
+          </cell>
+          <cell r="BA1">
+            <v>0.23300000000000001</v>
+          </cell>
+          <cell r="BB1">
+            <v>0.46400000000000002</v>
+          </cell>
+          <cell r="BC1">
+            <v>0.35699999999999998</v>
+          </cell>
+          <cell r="BD1">
+            <v>0.36599999999999999</v>
+          </cell>
+          <cell r="BE1">
+            <v>0.44500000000000001</v>
+          </cell>
+          <cell r="BF1">
+            <v>0.36099999999999999</v>
+          </cell>
+          <cell r="BG1">
+            <v>0.60199999999999998</v>
+          </cell>
+          <cell r="BH1">
+            <v>0.47799999999999998</v>
+          </cell>
+          <cell r="BI1">
+            <v>0.26400000000000001</v>
+          </cell>
+          <cell r="BJ1">
+            <v>0.56999999999999995</v>
+          </cell>
+          <cell r="BK1">
+            <v>0.35199999999999998</v>
+          </cell>
+          <cell r="BL1">
+            <v>0.54900000000000004</v>
+          </cell>
+          <cell r="BM1">
+            <v>0.22800000000000001</v>
+          </cell>
+          <cell r="BN1">
+            <v>0.68200000000000005</v>
+          </cell>
+          <cell r="BO1">
+            <v>0.36699999999999999</v>
+          </cell>
+          <cell r="BP1">
+            <v>0.32</v>
+          </cell>
+          <cell r="BQ1">
+            <v>0.41399999999999998</v>
+          </cell>
+          <cell r="BR1">
+            <v>0.19500000000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="yearl_h22_WO"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1">
+            <v>-3.2010000000000001</v>
+          </cell>
+          <cell r="B1">
+            <v>-2.6080000000000001</v>
+          </cell>
+          <cell r="C1">
+            <v>-4.6130000000000004</v>
+          </cell>
+          <cell r="D1">
+            <v>-1.5329999999999999</v>
+          </cell>
+          <cell r="E1">
+            <v>-2.1890000000000001</v>
+          </cell>
+          <cell r="F1">
+            <v>-1.4419999999999999</v>
+          </cell>
+          <cell r="G1">
+            <v>-2.1150000000000002</v>
+          </cell>
+          <cell r="H1">
+            <v>-1.075</v>
+          </cell>
+          <cell r="I1">
+            <v>-2.2719999999999998</v>
+          </cell>
+          <cell r="J1">
+            <v>-3.121</v>
+          </cell>
+          <cell r="K1">
+            <v>-3.06</v>
+          </cell>
+          <cell r="L1">
+            <v>-3.944</v>
+          </cell>
+          <cell r="M1">
+            <v>-4.3609999999999998</v>
+          </cell>
+          <cell r="N1">
+            <v>-5.7279999999999998</v>
+          </cell>
+          <cell r="O1">
+            <v>-4.4809999999999999</v>
+          </cell>
+          <cell r="P1">
+            <v>-5.298</v>
+          </cell>
+          <cell r="Q1">
+            <v>-3.7669999999999999</v>
+          </cell>
+          <cell r="R1">
+            <v>-5.2389999999999999</v>
+          </cell>
+          <cell r="S1">
+            <v>-3.5190000000000001</v>
+          </cell>
+          <cell r="T1">
+            <v>-2.7749999999999999</v>
+          </cell>
+          <cell r="U1">
+            <v>-1.5509999999999999</v>
+          </cell>
+          <cell r="V1">
+            <v>-2.6030000000000002</v>
+          </cell>
+          <cell r="W1">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="X1">
+            <v>5.1999999999999998E-2</v>
+          </cell>
+          <cell r="Y1">
+            <v>-0.96</v>
+          </cell>
+          <cell r="Z1">
+            <v>1.091</v>
+          </cell>
+          <cell r="AA1">
+            <v>0.122</v>
+          </cell>
+          <cell r="AB1">
+            <v>-2.306</v>
+          </cell>
+          <cell r="AC1">
+            <v>-2.7629999999999999</v>
+          </cell>
+          <cell r="AD1">
+            <v>-0.45900000000000002</v>
+          </cell>
+          <cell r="AE1">
+            <v>0.11</v>
+          </cell>
+          <cell r="AF1">
+            <v>-1.0369999999999999</v>
+          </cell>
+          <cell r="AG1">
+            <v>-0.89300000000000002</v>
+          </cell>
+          <cell r="AH1">
+            <v>1.0880000000000001</v>
+          </cell>
+          <cell r="AI1">
+            <v>0.90300000000000002</v>
+          </cell>
+          <cell r="AJ1">
+            <v>0.17699999999999999</v>
+          </cell>
+          <cell r="AK1">
+            <v>2.6459999999999999</v>
+          </cell>
+          <cell r="AL1">
+            <v>0.57199999999999995</v>
+          </cell>
+          <cell r="AM1">
+            <v>0.68400000000000005</v>
+          </cell>
+          <cell r="AN1">
+            <v>1.51</v>
+          </cell>
+          <cell r="AO1">
+            <v>2.2639999999999998</v>
+          </cell>
+          <cell r="AP1">
+            <v>4.5439999999999996</v>
+          </cell>
+          <cell r="AQ1">
+            <v>3.2450000000000001</v>
+          </cell>
+          <cell r="AR1">
+            <v>4.3040000000000003</v>
+          </cell>
+          <cell r="AS1">
+            <v>5.9429999999999996</v>
+          </cell>
+          <cell r="AT1">
+            <v>5.6719999999999997</v>
+          </cell>
+          <cell r="AU1">
+            <v>4.117</v>
+          </cell>
+          <cell r="AV1">
+            <v>6.7889999999999997</v>
+          </cell>
+          <cell r="AW1">
+            <v>9.952</v>
+          </cell>
+          <cell r="AX1">
+            <v>10.24</v>
+          </cell>
+          <cell r="AY1">
+            <v>8.4120000000000008</v>
+          </cell>
+          <cell r="AZ1">
+            <v>10.43</v>
+          </cell>
+          <cell r="BA1">
+            <v>9.4779999999999998</v>
+          </cell>
+          <cell r="BB1">
+            <v>10.052</v>
+          </cell>
+          <cell r="BC1">
+            <v>10.125999999999999</v>
+          </cell>
+          <cell r="BD1">
+            <v>10.367000000000001</v>
+          </cell>
+          <cell r="BE1">
+            <v>10.869</v>
+          </cell>
+          <cell r="BF1">
+            <v>10.941000000000001</v>
+          </cell>
+          <cell r="BG1">
+            <v>12.601000000000001</v>
+          </cell>
+          <cell r="BH1">
+            <v>13.260999999999999</v>
+          </cell>
+          <cell r="BI1">
+            <v>15.122</v>
+          </cell>
+          <cell r="BJ1">
+            <v>13.972</v>
+          </cell>
+          <cell r="BK1">
+            <v>15.878</v>
+          </cell>
+          <cell r="BL1">
+            <v>16.722000000000001</v>
+          </cell>
+          <cell r="BM1">
+            <v>17.725999999999999</v>
+          </cell>
+          <cell r="BN1">
+            <v>17.524000000000001</v>
+          </cell>
+          <cell r="BO1">
+            <v>18.734999999999999</v>
+          </cell>
+          <cell r="BP1">
+            <v>19.687000000000001</v>
+          </cell>
+          <cell r="BQ1">
+            <v>20.731999999999999</v>
+          </cell>
+          <cell r="BR1">
+            <v>21.469000000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="yearl_h22_WO2000"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1">
+            <v>10.170999999999999</v>
+          </cell>
+          <cell r="B1">
+            <v>12.638</v>
+          </cell>
+          <cell r="C1">
+            <v>12.394</v>
+          </cell>
+          <cell r="D1">
+            <v>13.257</v>
+          </cell>
+          <cell r="E1">
+            <v>13.430999999999999</v>
+          </cell>
+          <cell r="F1">
+            <v>14.537000000000001</v>
+          </cell>
+          <cell r="G1">
+            <v>15.394</v>
+          </cell>
+          <cell r="H1">
+            <v>16.187000000000001</v>
+          </cell>
+          <cell r="I1">
+            <v>18.649999999999999</v>
+          </cell>
+          <cell r="J1">
+            <v>20.11</v>
+          </cell>
+          <cell r="K1">
+            <v>22.401</v>
+          </cell>
+          <cell r="L1">
+            <v>20.798999999999999</v>
+          </cell>
+          <cell r="M1">
+            <v>23.588999999999999</v>
+          </cell>
+          <cell r="N1">
+            <v>24.059000000000001</v>
+          </cell>
+          <cell r="O1">
+            <v>25.436</v>
+          </cell>
+          <cell r="P1">
+            <v>25.524999999999999</v>
+          </cell>
+          <cell r="Q1">
+            <v>27.28</v>
+          </cell>
+          <cell r="R1">
+            <v>28.192</v>
+          </cell>
+          <cell r="S1">
+            <v>29.22</v>
+          </cell>
+          <cell r="T1">
+            <v>30.315999999999999</v>
+          </cell>
+          <cell r="U1">
+            <v>32.533000000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="yearl_h22_se_WO2000"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1">
+            <v>0.83499999999999996</v>
+          </cell>
+          <cell r="B1">
+            <v>0.32700000000000001</v>
+          </cell>
+          <cell r="C1">
+            <v>0.434</v>
+          </cell>
+          <cell r="D1">
+            <v>0.51900000000000002</v>
+          </cell>
+          <cell r="E1">
+            <v>0.63600000000000001</v>
+          </cell>
+          <cell r="F1">
+            <v>0.52700000000000002</v>
+          </cell>
+          <cell r="G1">
+            <v>0.50700000000000001</v>
+          </cell>
+          <cell r="H1">
+            <v>0.47299999999999998</v>
+          </cell>
+          <cell r="I1">
+            <v>1.0589999999999999</v>
+          </cell>
+          <cell r="J1">
+            <v>0.58899999999999997</v>
+          </cell>
+          <cell r="K1">
+            <v>0.38500000000000001</v>
+          </cell>
+          <cell r="L1">
+            <v>0.83199999999999996</v>
+          </cell>
+          <cell r="M1">
+            <v>0.56299999999999994</v>
+          </cell>
+          <cell r="N1">
+            <v>0.82799999999999996</v>
+          </cell>
+          <cell r="O1">
+            <v>0.28699999999999998</v>
+          </cell>
+          <cell r="P1">
+            <v>0.92400000000000004</v>
+          </cell>
+          <cell r="Q1">
+            <v>0.36799999999999999</v>
+          </cell>
+          <cell r="R1">
+            <v>0.25</v>
+          </cell>
+          <cell r="S1">
+            <v>0.54600000000000004</v>
+          </cell>
+          <cell r="T1">
+            <v>0.189</v>
+          </cell>
+          <cell r="U1">
+            <v>0.26700000000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -422,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4E9149-7520-8540-9CF8-8624DDC29FEB}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:DI116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -430,7 +1080,7 @@
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,18 +1097,335 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1955.5</v>
       </c>
-      <c r="B2">
+      <c r="B2" cm="1">
+        <f t="array" ref="B2:C116">TRANSPOSE(I2:DS3)</f>
         <v>-3.2010000000000001</v>
       </c>
       <c r="C2">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I2" cm="1">
+        <f t="array" ref="I2:DI2">[2]yearl_h22_WO!$A$1:$DA$1</f>
+        <v>-3.2010000000000001</v>
+      </c>
+      <c r="J2">
+        <v>-2.6080000000000001</v>
+      </c>
+      <c r="K2">
+        <v>-4.6130000000000004</v>
+      </c>
+      <c r="L2">
+        <v>-1.5329999999999999</v>
+      </c>
+      <c r="M2">
+        <v>-2.1890000000000001</v>
+      </c>
+      <c r="N2">
+        <v>-1.4419999999999999</v>
+      </c>
+      <c r="O2">
+        <v>-2.1150000000000002</v>
+      </c>
+      <c r="P2">
+        <v>-1.075</v>
+      </c>
+      <c r="Q2">
+        <v>-2.2719999999999998</v>
+      </c>
+      <c r="R2">
+        <v>-3.121</v>
+      </c>
+      <c r="S2">
+        <v>-3.06</v>
+      </c>
+      <c r="T2">
+        <v>-3.944</v>
+      </c>
+      <c r="U2">
+        <v>-4.3609999999999998</v>
+      </c>
+      <c r="V2">
+        <v>-5.7279999999999998</v>
+      </c>
+      <c r="W2">
+        <v>-4.4809999999999999</v>
+      </c>
+      <c r="X2">
+        <v>-5.298</v>
+      </c>
+      <c r="Y2">
+        <v>-3.7669999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>-5.2389999999999999</v>
+      </c>
+      <c r="AA2">
+        <v>-3.5190000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>-2.7749999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>-1.5509999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>-2.6030000000000002</v>
+      </c>
+      <c r="AE2">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AF2">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="AG2">
+        <v>-0.96</v>
+      </c>
+      <c r="AH2">
+        <v>1.091</v>
+      </c>
+      <c r="AI2">
+        <v>0.122</v>
+      </c>
+      <c r="AJ2">
+        <v>-2.306</v>
+      </c>
+      <c r="AK2">
+        <v>-2.7629999999999999</v>
+      </c>
+      <c r="AL2">
+        <v>-0.45900000000000002</v>
+      </c>
+      <c r="AM2">
+        <v>0.11</v>
+      </c>
+      <c r="AN2">
+        <v>-1.0369999999999999</v>
+      </c>
+      <c r="AO2">
+        <v>-0.89300000000000002</v>
+      </c>
+      <c r="AP2">
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="AR2">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="AU2">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="AV2">
+        <v>1.51</v>
+      </c>
+      <c r="AW2">
+        <v>2.2639999999999998</v>
+      </c>
+      <c r="AX2">
+        <v>4.5439999999999996</v>
+      </c>
+      <c r="AY2">
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>4.3040000000000003</v>
+      </c>
+      <c r="BA2">
+        <v>5.9429999999999996</v>
+      </c>
+      <c r="BB2">
+        <v>5.6719999999999997</v>
+      </c>
+      <c r="BC2">
+        <v>4.117</v>
+      </c>
+      <c r="BD2">
+        <v>6.7889999999999997</v>
+      </c>
+      <c r="BE2">
+        <v>9.952</v>
+      </c>
+      <c r="BF2">
+        <v>10.24</v>
+      </c>
+      <c r="BG2">
+        <v>8.4120000000000008</v>
+      </c>
+      <c r="BH2">
+        <v>10.43</v>
+      </c>
+      <c r="BI2">
+        <v>9.4779999999999998</v>
+      </c>
+      <c r="BJ2">
+        <v>10.052</v>
+      </c>
+      <c r="BK2">
+        <v>10.125999999999999</v>
+      </c>
+      <c r="BL2">
+        <v>10.367000000000001</v>
+      </c>
+      <c r="BM2">
+        <v>10.869</v>
+      </c>
+      <c r="BN2">
+        <v>10.941000000000001</v>
+      </c>
+      <c r="BO2">
+        <v>12.601000000000001</v>
+      </c>
+      <c r="BP2">
+        <v>13.260999999999999</v>
+      </c>
+      <c r="BQ2">
+        <v>15.122</v>
+      </c>
+      <c r="BR2">
+        <v>13.972</v>
+      </c>
+      <c r="BS2">
+        <v>15.878</v>
+      </c>
+      <c r="BT2">
+        <v>16.722000000000001</v>
+      </c>
+      <c r="BU2">
+        <v>17.725999999999999</v>
+      </c>
+      <c r="BV2">
+        <v>17.524000000000001</v>
+      </c>
+      <c r="BW2">
+        <v>18.734999999999999</v>
+      </c>
+      <c r="BX2">
+        <v>19.687000000000001</v>
+      </c>
+      <c r="BY2">
+        <v>20.731999999999999</v>
+      </c>
+      <c r="BZ2">
+        <v>21.469000000000001</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
+        <v>0</v>
+      </c>
+      <c r="CC2">
+        <v>0</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
+      </c>
+      <c r="CE2">
+        <v>0</v>
+      </c>
+      <c r="CF2">
+        <v>0</v>
+      </c>
+      <c r="CG2">
+        <v>0</v>
+      </c>
+      <c r="CH2">
+        <v>0</v>
+      </c>
+      <c r="CI2">
+        <v>0</v>
+      </c>
+      <c r="CJ2">
+        <v>0</v>
+      </c>
+      <c r="CK2">
+        <v>0</v>
+      </c>
+      <c r="CL2">
+        <v>0</v>
+      </c>
+      <c r="CM2">
+        <v>0</v>
+      </c>
+      <c r="CN2">
+        <v>0</v>
+      </c>
+      <c r="CO2">
+        <v>0</v>
+      </c>
+      <c r="CP2">
+        <v>0</v>
+      </c>
+      <c r="CQ2">
+        <v>0</v>
+      </c>
+      <c r="CR2">
+        <v>0</v>
+      </c>
+      <c r="CS2">
+        <v>0</v>
+      </c>
+      <c r="CT2">
+        <v>0</v>
+      </c>
+      <c r="CU2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>0</v>
+      </c>
+      <c r="CW2">
+        <v>0</v>
+      </c>
+      <c r="CX2">
+        <v>0</v>
+      </c>
+      <c r="CY2">
+        <v>0</v>
+      </c>
+      <c r="CZ2">
+        <v>0</v>
+      </c>
+      <c r="DA2">
+        <v>0</v>
+      </c>
+      <c r="DB2">
+        <v>0</v>
+      </c>
+      <c r="DC2">
+        <v>0</v>
+      </c>
+      <c r="DD2">
+        <v>0</v>
+      </c>
+      <c r="DE2">
+        <v>0</v>
+      </c>
+      <c r="DF2">
+        <v>0</v>
+      </c>
+      <c r="DG2">
+        <v>0</v>
+      </c>
+      <c r="DH2">
+        <v>0</v>
+      </c>
+      <c r="DI2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A3">
         <f>A2+1</f>
         <v>1956.5</v>
@@ -469,8 +1436,324 @@
       <c r="C3">
         <v>0.71899999999999997</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I3" cm="1">
+        <f t="array" ref="I3:DI3">[1]yearl_h22_se_WO!$A$1:$DA$1</f>
+        <v>1.7</v>
+      </c>
+      <c r="J3">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="K3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="L3">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="M3">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="N3">
+        <v>0.499</v>
+      </c>
+      <c r="O3">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="P3">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="Q3">
+        <v>0.65</v>
+      </c>
+      <c r="R3">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="S3">
+        <v>0.307</v>
+      </c>
+      <c r="T3">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="U3">
+        <v>0.372</v>
+      </c>
+      <c r="V3">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="W3">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="X3">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="Y3">
+        <v>0.51</v>
+      </c>
+      <c r="Z3">
+        <v>1.1539999999999999</v>
+      </c>
+      <c r="AA3">
+        <v>1.256</v>
+      </c>
+      <c r="AB3">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="AC3">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="AD3">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="AE3">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="AF3">
+        <v>0.432</v>
+      </c>
+      <c r="AG3">
+        <v>0.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="AI3">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="AJ3">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="AK3">
+        <v>1.871</v>
+      </c>
+      <c r="AL3">
+        <v>1.262</v>
+      </c>
+      <c r="AM3">
+        <v>1.2270000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>1.109</v>
+      </c>
+      <c r="AO3">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="AP3">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="AR3">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="AS3">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="AT3">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="AU3">
+        <v>0.439</v>
+      </c>
+      <c r="AV3">
+        <v>0.746</v>
+      </c>
+      <c r="AW3">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="AX3">
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="AY3">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="AZ3">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="BA3">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="BB3">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="BC3">
+        <v>1.115</v>
+      </c>
+      <c r="BD3">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="BE3">
+        <v>0.622</v>
+      </c>
+      <c r="BF3">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="BG3">
+        <v>0.317</v>
+      </c>
+      <c r="BH3">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="BI3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="BJ3">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="BK3">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="BL3">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="BM3">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="BN3">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="BO3">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="BP3">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="BQ3">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="BR3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="BS3">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="BT3">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="BU3">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="BV3">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="BW3">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="BX3">
+        <v>0.32</v>
+      </c>
+      <c r="BY3">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="BZ3">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
+      <c r="CC3">
+        <v>0</v>
+      </c>
+      <c r="CD3">
+        <v>0</v>
+      </c>
+      <c r="CE3">
+        <v>0</v>
+      </c>
+      <c r="CF3">
+        <v>0</v>
+      </c>
+      <c r="CG3">
+        <v>0</v>
+      </c>
+      <c r="CH3">
+        <v>0</v>
+      </c>
+      <c r="CI3">
+        <v>0</v>
+      </c>
+      <c r="CJ3">
+        <v>0</v>
+      </c>
+      <c r="CK3">
+        <v>0</v>
+      </c>
+      <c r="CL3">
+        <v>0</v>
+      </c>
+      <c r="CM3">
+        <v>0</v>
+      </c>
+      <c r="CN3">
+        <v>0</v>
+      </c>
+      <c r="CO3">
+        <v>0</v>
+      </c>
+      <c r="CP3">
+        <v>0</v>
+      </c>
+      <c r="CQ3">
+        <v>0</v>
+      </c>
+      <c r="CR3">
+        <v>0</v>
+      </c>
+      <c r="CS3">
+        <v>0</v>
+      </c>
+      <c r="CT3">
+        <v>0</v>
+      </c>
+      <c r="CU3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>0</v>
+      </c>
+      <c r="CW3">
+        <v>0</v>
+      </c>
+      <c r="CX3">
+        <v>0</v>
+      </c>
+      <c r="CY3">
+        <v>0</v>
+      </c>
+      <c r="CZ3">
+        <v>0</v>
+      </c>
+      <c r="DA3">
+        <v>0</v>
+      </c>
+      <c r="DB3">
+        <v>0</v>
+      </c>
+      <c r="DC3">
+        <v>0</v>
+      </c>
+      <c r="DD3">
+        <v>0</v>
+      </c>
+      <c r="DE3">
+        <v>0</v>
+      </c>
+      <c r="DF3">
+        <v>0</v>
+      </c>
+      <c r="DG3">
+        <v>0</v>
+      </c>
+      <c r="DH3">
+        <v>0</v>
+      </c>
+      <c r="DI3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>1957.5</v>
@@ -482,7 +1765,7 @@
         <v>0.39600000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1958.5</v>
@@ -494,7 +1777,7 @@
         <v>0.68700000000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1959.5</v>
@@ -505,8 +1788,324 @@
       <c r="C6">
         <v>0.86299999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I6" cm="1">
+        <f t="array" ref="I6:DI6">[3]yearl_h22_WO2000!$A$1:$DA$1</f>
+        <v>10.170999999999999</v>
+      </c>
+      <c r="J6">
+        <v>12.638</v>
+      </c>
+      <c r="K6">
+        <v>12.394</v>
+      </c>
+      <c r="L6">
+        <v>13.257</v>
+      </c>
+      <c r="M6">
+        <v>13.430999999999999</v>
+      </c>
+      <c r="N6">
+        <v>14.537000000000001</v>
+      </c>
+      <c r="O6">
+        <v>15.394</v>
+      </c>
+      <c r="P6">
+        <v>16.187000000000001</v>
+      </c>
+      <c r="Q6">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="R6">
+        <v>20.11</v>
+      </c>
+      <c r="S6">
+        <v>22.401</v>
+      </c>
+      <c r="T6">
+        <v>20.798999999999999</v>
+      </c>
+      <c r="U6">
+        <v>23.588999999999999</v>
+      </c>
+      <c r="V6">
+        <v>24.059000000000001</v>
+      </c>
+      <c r="W6">
+        <v>25.436</v>
+      </c>
+      <c r="X6">
+        <v>25.524999999999999</v>
+      </c>
+      <c r="Y6">
+        <v>27.28</v>
+      </c>
+      <c r="Z6">
+        <v>28.192</v>
+      </c>
+      <c r="AA6">
+        <v>29.22</v>
+      </c>
+      <c r="AB6">
+        <v>30.315999999999999</v>
+      </c>
+      <c r="AC6">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
+        <v>0</v>
+      </c>
+      <c r="CC6">
+        <v>0</v>
+      </c>
+      <c r="CD6">
+        <v>0</v>
+      </c>
+      <c r="CE6">
+        <v>0</v>
+      </c>
+      <c r="CF6">
+        <v>0</v>
+      </c>
+      <c r="CG6">
+        <v>0</v>
+      </c>
+      <c r="CH6">
+        <v>0</v>
+      </c>
+      <c r="CI6">
+        <v>0</v>
+      </c>
+      <c r="CJ6">
+        <v>0</v>
+      </c>
+      <c r="CK6">
+        <v>0</v>
+      </c>
+      <c r="CL6">
+        <v>0</v>
+      </c>
+      <c r="CM6">
+        <v>0</v>
+      </c>
+      <c r="CN6">
+        <v>0</v>
+      </c>
+      <c r="CO6">
+        <v>0</v>
+      </c>
+      <c r="CP6">
+        <v>0</v>
+      </c>
+      <c r="CQ6">
+        <v>0</v>
+      </c>
+      <c r="CR6">
+        <v>0</v>
+      </c>
+      <c r="CS6">
+        <v>0</v>
+      </c>
+      <c r="CT6">
+        <v>0</v>
+      </c>
+      <c r="CU6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>0</v>
+      </c>
+      <c r="CW6">
+        <v>0</v>
+      </c>
+      <c r="CX6">
+        <v>0</v>
+      </c>
+      <c r="CY6">
+        <v>0</v>
+      </c>
+      <c r="CZ6">
+        <v>0</v>
+      </c>
+      <c r="DA6">
+        <v>0</v>
+      </c>
+      <c r="DB6">
+        <v>0</v>
+      </c>
+      <c r="DC6">
+        <v>0</v>
+      </c>
+      <c r="DD6">
+        <v>0</v>
+      </c>
+      <c r="DE6">
+        <v>0</v>
+      </c>
+      <c r="DF6">
+        <v>0</v>
+      </c>
+      <c r="DG6">
+        <v>0</v>
+      </c>
+      <c r="DH6">
+        <v>0</v>
+      </c>
+      <c r="DI6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1960.5</v>
@@ -517,8 +2116,324 @@
       <c r="C7">
         <v>0.499</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I7" cm="1">
+        <f t="array" ref="I7:DI7">[4]yearl_h22_se_WO2000!$A$1:$DA$1</f>
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="J7">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="K7">
+        <v>0.434</v>
+      </c>
+      <c r="L7">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="M7">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="O7">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="P7">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="Q7">
+        <v>1.0589999999999999</v>
+      </c>
+      <c r="R7">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="S7">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="T7">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="U7">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="V7">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="W7">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="X7">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="Y7">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="Z7">
+        <v>0.25</v>
+      </c>
+      <c r="AA7">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="AB7">
+        <v>0.189</v>
+      </c>
+      <c r="AC7">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7">
+        <v>0</v>
+      </c>
+      <c r="CC7">
+        <v>0</v>
+      </c>
+      <c r="CD7">
+        <v>0</v>
+      </c>
+      <c r="CE7">
+        <v>0</v>
+      </c>
+      <c r="CF7">
+        <v>0</v>
+      </c>
+      <c r="CG7">
+        <v>0</v>
+      </c>
+      <c r="CH7">
+        <v>0</v>
+      </c>
+      <c r="CI7">
+        <v>0</v>
+      </c>
+      <c r="CJ7">
+        <v>0</v>
+      </c>
+      <c r="CK7">
+        <v>0</v>
+      </c>
+      <c r="CL7">
+        <v>0</v>
+      </c>
+      <c r="CM7">
+        <v>0</v>
+      </c>
+      <c r="CN7">
+        <v>0</v>
+      </c>
+      <c r="CO7">
+        <v>0</v>
+      </c>
+      <c r="CP7">
+        <v>0</v>
+      </c>
+      <c r="CQ7">
+        <v>0</v>
+      </c>
+      <c r="CR7">
+        <v>0</v>
+      </c>
+      <c r="CS7">
+        <v>0</v>
+      </c>
+      <c r="CT7">
+        <v>0</v>
+      </c>
+      <c r="CU7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
+      </c>
+      <c r="CW7">
+        <v>0</v>
+      </c>
+      <c r="CX7">
+        <v>0</v>
+      </c>
+      <c r="CY7">
+        <v>0</v>
+      </c>
+      <c r="CZ7">
+        <v>0</v>
+      </c>
+      <c r="DA7">
+        <v>0</v>
+      </c>
+      <c r="DB7">
+        <v>0</v>
+      </c>
+      <c r="DC7">
+        <v>0</v>
+      </c>
+      <c r="DD7">
+        <v>0</v>
+      </c>
+      <c r="DE7">
+        <v>0</v>
+      </c>
+      <c r="DF7">
+        <v>0</v>
+      </c>
+      <c r="DG7">
+        <v>0</v>
+      </c>
+      <c r="DH7">
+        <v>0</v>
+      </c>
+      <c r="DI7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1961.5</v>
@@ -529,8 +2444,87 @@
       <c r="C8">
         <v>0.42099999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>2005.5</v>
+      </c>
+      <c r="J8">
+        <f>I8+1</f>
+        <v>2006.5</v>
+      </c>
+      <c r="K8">
+        <f t="shared" ref="K8:AB8" si="1">J8+1</f>
+        <v>2007.5</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>2008.5</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="1"/>
+        <v>2009.5</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>2010.5</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>2011.5</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>2012.5</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="1"/>
+        <v>2013.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>2014.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="1"/>
+        <v>2015.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="1"/>
+        <v>2016.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="1"/>
+        <v>2017.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="1"/>
+        <v>2018.5</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="1"/>
+        <v>2019.5</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="1"/>
+        <v>2020.5</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="1"/>
+        <v>2021.5</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="1"/>
+        <v>2022.5</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="1"/>
+        <v>2023.5</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="1"/>
+        <v>2024.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1962.5</v>
@@ -542,7 +2536,7 @@
         <v>0.94699999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1963.5</v>
@@ -554,7 +2548,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1964.5</v>
@@ -566,7 +2560,7 @@
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1965.5</v>
@@ -578,7 +2572,7 @@
         <v>0.307</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>1966.5</v>
@@ -590,7 +2584,7 @@
         <v>0.45600000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>1967.5</v>
@@ -602,7 +2596,7 @@
         <v>0.372</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>1968.5</v>
@@ -614,7 +2608,7 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>1969.5</v>
@@ -1057,7 +3051,8 @@
       <c r="C52">
         <v>0.317</v>
       </c>
-      <c r="D52">
+      <c r="D52" cm="1">
+        <f t="array" ref="D52:E116">TRANSPOSE(I6:BU7)</f>
         <v>10.170999999999999</v>
       </c>
       <c r="E52">
@@ -1336,7 +3331,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" ref="A68:A71" si="1">A67+1</f>
+        <f t="shared" ref="A68:A72" si="2">A67+1</f>
         <v>2021.5</v>
       </c>
       <c r="B68">
@@ -1354,7 +3349,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2022.5</v>
       </c>
       <c r="B69">
@@ -1372,7 +3367,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2023.5</v>
       </c>
       <c r="B70">
@@ -1390,7 +3385,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2024.5</v>
       </c>
       <c r="B71">
@@ -1404,6 +3399,640 @@
       </c>
       <c r="E71">
         <v>0.189</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <f t="shared" si="2"/>
+        <v>2025.5</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="E72">
+        <v>0.26700000000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
